--- a/output/pdf_financials_xlsx/SVA.xlsx
+++ b/output/pdf_financials_xlsx/SVA.xlsx
@@ -1312,40 +1312,40 @@
         <v>-1.846371</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.028278</v>
+        <v>-2.028278</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.568028</v>
+        <v>-2.568028</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.002921</v>
+        <v>-2.002921</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.746059</v>
+        <v>-2.746059</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.026211</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.499622</v>
+        <v>-2.499622</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.639479</v>
+        <v>-2.639479</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.698627</v>
+        <v>-3.698627</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>3.971272</v>
+        <v>-3.971272</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>24.420536</v>
+        <v>-24.420536</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>38.99752</v>
@@ -1409,7 +1409,7 @@
         <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-77.99504</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0.007</v>
@@ -1628,49 +1628,49 @@
         <v>-1.846371</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.028278</v>
+        <v>-2.028278</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.568028</v>
+        <v>-2.568028</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.002921</v>
+        <v>-2.002921</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.746059</v>
+        <v>-2.746059</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.026211</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.499622</v>
+        <v>-2.499622</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.639479</v>
+        <v>-2.639479</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.698627</v>
+        <v>-3.698627</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>3.971272</v>
+        <v>-3.971272</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>24.420536</v>
+        <v>-24.420536</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>38.99752</v>
+        <v>-38.99752</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>32.192135</v>
+        <v>-32.192135</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>15.743466</v>
+        <v>-15.743466</v>
       </c>
     </row>
     <row r="21">
@@ -1811,49 +1811,49 @@
         <v>-1.846371</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.028278</v>
+        <v>-2.028278</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.568028</v>
+        <v>-2.568028</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.002921</v>
+        <v>-2.002921</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.746059</v>
+        <v>-2.746059</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.026211</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.499622</v>
+        <v>-2.499622</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.639479</v>
+        <v>-2.639479</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.698627</v>
+        <v>-3.698627</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>3.971272</v>
+        <v>-3.971272</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>24.420536</v>
+        <v>-24.420536</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>38.99752</v>
+        <v>-38.99752</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>32.192135</v>
+        <v>-32.192135</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>15.743466</v>
+        <v>-15.743466</v>
       </c>
     </row>
     <row r="24">
@@ -2010,31 +2010,31 @@
         <v>61.5457</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-101.4139</v>
+        <v>101.4139</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-128.4014</v>
+        <v>128.4014</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-100.14605</v>
+        <v>100.14605</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>137.30295</v>
+        <v>-137.30295</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>-1.31055</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>124.9811</v>
+        <v>-124.9811</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>131.97395</v>
+        <v>-131.97395</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>184.93135</v>
+        <v>-184.93135</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>198.5636</v>
+        <v>-198.5636</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>232.184633</v>
+        <v>-232.184633</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>271.339289</v>
+        <v>-271.339289</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2079,40 +2079,40 @@
         <v>-1.846371</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.045245</v>
+        <v>-2.011311</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.607339</v>
+        <v>-2.528717</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.066716</v>
+        <v>-1.939126</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.797187</v>
+        <v>-2.694931</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.005784</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.529735</v>
+        <v>-2.469509</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.693637</v>
+        <v>-2.585321</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.726376</v>
+        <v>-3.670878</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>3.971272</v>
+        <v>-3.971272</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>24.420536</v>
+        <v>-24.420536</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>38.99752</v>
@@ -2201,40 +2201,40 @@
         <v>-0.999453</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.915648</v>
+        <v>-1.140908</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.607339</v>
+        <v>-2.528717</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.066716</v>
+        <v>-1.939126</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.797187</v>
+        <v>-2.694931</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.005784</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.529735</v>
+        <v>-2.469509</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.693637</v>
+        <v>-2.585321</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.790905</v>
+        <v>-3.606349</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>4.032747</v>
+        <v>-3.909797</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>7.232743</v>
+        <v>-6.698335</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>24.860534</v>
+        <v>-23.980538</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>39.443071</v>
@@ -2359,43 +2359,43 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>0.02174917085169908</v>
@@ -39352,10 +39352,10 @@
         </is>
       </c>
       <c r="U290" s="5" t="n">
-        <v>32.192135</v>
+        <v>-32.192135</v>
       </c>
       <c r="V290" s="5" t="n">
-        <v>15.743466</v>
+        <v>-15.743466</v>
       </c>
     </row>
     <row r="291">
@@ -40937,10 +40937,10 @@
         </is>
       </c>
       <c r="T305" s="5" t="n">
-        <v>38.99752</v>
+        <v>-38.99752</v>
       </c>
       <c r="U305" s="5" t="n">
-        <v>32.192135</v>
+        <v>-32.192135</v>
       </c>
       <c r="V305" t="inlineStr">
         <is>
@@ -42395,10 +42395,10 @@
         </is>
       </c>
       <c r="R319" s="5" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="S319" s="5" t="n">
-        <v>24.420536</v>
+        <v>-24.420536</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -43432,10 +43432,10 @@
         </is>
       </c>
       <c r="Q329" s="5" t="n">
-        <v>5.321308</v>
+        <v>-5.321308</v>
       </c>
       <c r="R329" s="5" t="n">
-        <v>6.965539</v>
+        <v>-6.965539</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
@@ -44054,10 +44054,10 @@
         </is>
       </c>
       <c r="O335" s="5" t="n">
-        <v>3.698627</v>
+        <v>-3.698627</v>
       </c>
       <c r="P335" s="5" t="n">
-        <v>3.971272</v>
+        <v>-3.971272</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -44762,13 +44762,13 @@
         </is>
       </c>
       <c r="M342" s="5" t="n">
-        <v>2.499622</v>
+        <v>-2.499622</v>
       </c>
       <c r="N342" s="5" t="n">
-        <v>2.639479</v>
+        <v>-2.639479</v>
       </c>
       <c r="O342" s="5" t="n">
-        <v>3.698627</v>
+        <v>-3.698627</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -45553,22 +45553,22 @@
         </is>
       </c>
       <c r="H350" s="5" t="n">
-        <v>2.028278</v>
+        <v>-2.028278</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>2.568028</v>
+        <v>-2.568028</v>
       </c>
       <c r="J350" s="5" t="n">
-        <v>2.002921</v>
+        <v>-2.002921</v>
       </c>
       <c r="K350" s="5" t="n">
-        <v>2.746059</v>
+        <v>-2.746059</v>
       </c>
       <c r="L350" s="5" t="n">
-        <v>2.859477</v>
+        <v>-2.859477</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>2.499622</v>
+        <v>-2.499622</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>
@@ -45668,10 +45668,10 @@
         </is>
       </c>
       <c r="K351" s="5" t="n">
-        <v>2.746059</v>
+        <v>-2.746059</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>2.859477</v>
+        <v>-2.859477</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SVA.xlsx
+++ b/output/pdf_financials_xlsx/SVA.xlsx
@@ -979,7 +979,7 @@
         <v>6.936507</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>16.896624</v>
+        <v>24.753761</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>40.501593</v>
@@ -1040,7 +1040,7 @@
         <v>-6.936507</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-16.896624</v>
+        <v>-24.753761</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-40.501593</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.037721</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004061</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1092,25 +1092,25 @@
         <v>-0.027749</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038465</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.070552</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.577285</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-1.500222</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.388391</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025634</v>
       </c>
     </row>
     <row r="13">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.753485</v>
+        <v>-2.791206</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.468361</v>
+        <v>-1.472422</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.846371</v>
@@ -2103,25 +2103,25 @@
         <v>-3.670878</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.971272</v>
+        <v>-3.932807</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-5.321308</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.965539</v>
+        <v>-6.894987</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-24.420536</v>
+        <v>-23.843251</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>38.99752</v>
+        <v>40.497742</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>32.185135</v>
+        <v>32.573526</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>15.734035</v>
+        <v>15.759669</v>
       </c>
     </row>
     <row r="28">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.951253</v>
+        <v>-1.988974</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.639772</v>
+        <v>-0.643833</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.999453</v>
@@ -2225,25 +2225,25 @@
         <v>-3.606349</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.909797</v>
+        <v>-3.871332</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-5.321308</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.698335</v>
+        <v>-6.627783</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-23.980538</v>
+        <v>-23.403253</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>39.443071</v>
+        <v>40.943293</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32.725415</v>
+        <v>33.113806</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>16.076626</v>
+        <v>16.10226</v>
       </c>
     </row>
     <row r="30">
@@ -2515,25 +2515,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.461346</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.396963</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.735142</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.309991</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.255557</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.273605</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.463808</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.211938</v>
@@ -2545,28 +2545,28 @@
         <v>2.627513</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.739346</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.797138</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.949412</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>27.874198</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.776054</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.721835</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>6.012274</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.265004</v>
       </c>
     </row>
     <row r="35">
@@ -2637,25 +2637,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.461346</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.396963</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.735142</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.208119</v>
+        <v>1.51811</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4.104164</v>
+        <v>4.359721</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.702301</v>
+        <v>4.975906</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.952902</v>
+        <v>3.41671</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.880963</v>
@@ -2667,28 +2667,28 @@
         <v>3.631887</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.003974</v>
+        <v>2.74332</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2.006999</v>
+        <v>3.804137</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.949412</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>27.874198</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>46</v>
+        <v>49.776054</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>11.084</v>
+        <v>19.805835</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>6.012274</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.265004</v>
       </c>
     </row>
     <row r="37">
@@ -3369,25 +3369,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.467543</v>
+        <v>0.006197</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.429856</v>
+        <v>0.032893</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.766138</v>
+        <v>0.030996</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.32488</v>
+        <v>0.014889</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.345015</v>
+        <v>0.089458</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.404953</v>
+        <v>0.131348</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.505616</v>
+        <v>0.041808</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.023832</v>
@@ -3399,28 +3399,28 @@
         <v>0.039785</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.840606</v>
+        <v>0.10126</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.574998</v>
+        <v>0.77786</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.098516</v>
+        <v>0.149104</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>27.878398</v>
+        <v>0.0042</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.944066</v>
+        <v>0.168012</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.886499000000001</v>
+        <v>0.164664</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>6.171444</v>
+        <v>0.15917</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.400017</v>
+        <v>0.135013</v>
       </c>
     </row>
     <row r="49">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -38414,7 +38414,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -41806,7 +41806,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -41910,7 +41910,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -47684,7 +47684,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" s="5" t="n">

--- a/output/pdf_financials_xlsx/SVA.xlsx
+++ b/output/pdf_financials_xlsx/SVA.xlsx
@@ -6583,16 +6583,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.8022319999999999</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.828589</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.8469179999999999</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.870403</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -35786,7 +35786,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
@@ -46248,7 +46248,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">
